--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2657,6 +2657,424 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121561244</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>625167</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7209946</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121561246</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>625158</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7209781</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121561245</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>625079</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7209811</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121561247</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>625210</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7209708</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2761,7 +2761,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561246</v>
+        <v>121561247</v>
       </c>
       <c r="B20" t="n">
         <v>57355</v>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625158</v>
+        <v>625210</v>
       </c>
       <c r="R20" t="n">
-        <v>7209781</v>
+        <v>7209708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561247</v>
+        <v>121561246</v>
       </c>
       <c r="B22" t="n">
         <v>57355</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625210</v>
+        <v>625158</v>
       </c>
       <c r="R22" t="n">
-        <v>7209708</v>
+        <v>7209781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561244</v>
+        <v>121561246</v>
       </c>
       <c r="B19" t="n">
-        <v>57371</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,16 +2693,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625167</v>
+        <v>625158</v>
       </c>
       <c r="R19" t="n">
-        <v>7209946</v>
+        <v>7209781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561247</v>
+        <v>121561244</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,16 +2782,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2795,21 +2800,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625167</v>
       </c>
       <c r="R20" t="n">
-        <v>7209708</v>
+        <v>7209946</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561245</v>
+        <v>121561247</v>
       </c>
       <c r="B21" t="n">
-        <v>57371</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2902,16 +2902,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625079</v>
+        <v>625210</v>
       </c>
       <c r="R21" t="n">
-        <v>7209811</v>
+        <v>7209708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2970,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561246</v>
+        <v>121561245</v>
       </c>
       <c r="B22" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,16 +2991,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3004,21 +3009,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625158</v>
+        <v>625079</v>
       </c>
       <c r="R22" t="n">
-        <v>7209781</v>
+        <v>7209811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2766,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561244</v>
+        <v>121561247</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,16 +2782,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2800,16 +2800,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625167</v>
+        <v>625210</v>
       </c>
       <c r="R20" t="n">
-        <v>7209946</v>
+        <v>7209708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561247</v>
+        <v>121561245</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,16 +2889,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2902,21 +2907,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625210</v>
+        <v>625079</v>
       </c>
       <c r="R21" t="n">
-        <v>7209708</v>
+        <v>7209811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,7 +2975,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561245</v>
+        <v>121561244</v>
       </c>
       <c r="B22" t="n">
         <v>57372</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625079</v>
+        <v>625167</v>
       </c>
       <c r="R22" t="n">
-        <v>7209811</v>
+        <v>7209946</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2659,7 +2659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561246</v>
+        <v>121561247</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625158</v>
+        <v>625210</v>
       </c>
       <c r="R19" t="n">
-        <v>7209781</v>
+        <v>7209708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561247</v>
+        <v>121561246</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625158</v>
       </c>
       <c r="R20" t="n">
-        <v>7209708</v>
+        <v>7209781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,7 +2873,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561245</v>
+        <v>121561244</v>
       </c>
       <c r="B21" t="n">
         <v>57372</v>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625079</v>
+        <v>625167</v>
       </c>
       <c r="R21" t="n">
-        <v>7209811</v>
+        <v>7209946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,7 +2975,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561244</v>
+        <v>121561245</v>
       </c>
       <c r="B22" t="n">
         <v>57372</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625167</v>
+        <v>625079</v>
       </c>
       <c r="R22" t="n">
-        <v>7209946</v>
+        <v>7209811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561247</v>
+        <v>121561245</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,21 +2693,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625210</v>
+        <v>625079</v>
       </c>
       <c r="R19" t="n">
-        <v>7209708</v>
+        <v>7209811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2873,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561244</v>
+        <v>121561247</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,16 +2884,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2907,16 +2902,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625167</v>
+        <v>625210</v>
       </c>
       <c r="R21" t="n">
-        <v>7209946</v>
+        <v>7209708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,7 +2975,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561245</v>
+        <v>121561244</v>
       </c>
       <c r="B22" t="n">
         <v>57372</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625079</v>
+        <v>625167</v>
       </c>
       <c r="R22" t="n">
-        <v>7209811</v>
+        <v>7209946</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561244</v>
+        <v>121561246</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,16 +2693,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625167</v>
+        <v>625158</v>
       </c>
       <c r="R19" t="n">
-        <v>7209946</v>
+        <v>7209781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2970,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561246</v>
+        <v>121561244</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,16 +2991,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3004,21 +3009,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625158</v>
+        <v>625167</v>
       </c>
       <c r="R22" t="n">
-        <v>7209781</v>
+        <v>7209946</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561246</v>
+        <v>121561244</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,21 +2693,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625158</v>
+        <v>625167</v>
       </c>
       <c r="R19" t="n">
-        <v>7209781</v>
+        <v>7209946</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2868,7 +2863,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561247</v>
+        <v>121561246</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2913,10 +2908,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625210</v>
+        <v>625158</v>
       </c>
       <c r="R21" t="n">
-        <v>7209708</v>
+        <v>7209781</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,10 +2970,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561244</v>
+        <v>121561247</v>
       </c>
       <c r="B22" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,16 +2986,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3009,16 +3004,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625167</v>
+        <v>625210</v>
       </c>
       <c r="R22" t="n">
-        <v>7209946</v>
+        <v>7209708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561244</v>
+        <v>121561246</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,16 +2693,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625167</v>
+        <v>625158</v>
       </c>
       <c r="R19" t="n">
-        <v>7209946</v>
+        <v>7209781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561245</v>
+        <v>121561247</v>
       </c>
       <c r="B20" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,16 +2782,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2795,16 +2800,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625079</v>
+        <v>625210</v>
       </c>
       <c r="R20" t="n">
-        <v>7209811</v>
+        <v>7209708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561246</v>
+        <v>121561245</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2879,16 +2889,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2897,21 +2907,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625158</v>
+        <v>625079</v>
       </c>
       <c r="R21" t="n">
-        <v>7209781</v>
+        <v>7209811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2970,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561247</v>
+        <v>121561244</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,16 +2991,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3004,21 +3009,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625210</v>
+        <v>625167</v>
       </c>
       <c r="R22" t="n">
-        <v>7209708</v>
+        <v>7209946</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2766,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561247</v>
+        <v>121561244</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,16 +2782,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2800,21 +2800,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625167</v>
       </c>
       <c r="R20" t="n">
-        <v>7209708</v>
+        <v>7209946</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561245</v>
+        <v>121561247</v>
       </c>
       <c r="B21" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,16 +2884,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2907,16 +2902,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625079</v>
+        <v>625210</v>
       </c>
       <c r="R21" t="n">
-        <v>7209811</v>
+        <v>7209708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,7 +2975,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561244</v>
+        <v>121561245</v>
       </c>
       <c r="B22" t="n">
         <v>57373</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625167</v>
+        <v>625079</v>
       </c>
       <c r="R22" t="n">
-        <v>7209946</v>
+        <v>7209811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561246</v>
+        <v>121561245</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,21 +2693,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625158</v>
+        <v>625079</v>
       </c>
       <c r="R19" t="n">
-        <v>7209781</v>
+        <v>7209811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2766,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561244</v>
+        <v>121561247</v>
       </c>
       <c r="B20" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,16 +2777,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2800,16 +2795,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625167</v>
+        <v>625210</v>
       </c>
       <c r="R20" t="n">
-        <v>7209946</v>
+        <v>7209708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561247</v>
+        <v>121561244</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2902,21 +2902,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625210</v>
+        <v>625167</v>
       </c>
       <c r="R21" t="n">
-        <v>7209708</v>
+        <v>7209946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,10 +2970,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561245</v>
+        <v>121561246</v>
       </c>
       <c r="B22" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,16 +2986,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3009,16 +3004,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625079</v>
+        <v>625158</v>
       </c>
       <c r="R22" t="n">
-        <v>7209811</v>
+        <v>7209781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -2761,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561247</v>
+        <v>121561244</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,16 +2777,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2795,21 +2795,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625167</v>
       </c>
       <c r="R20" t="n">
-        <v>7209708</v>
+        <v>7209946</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,10 +2863,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561244</v>
+        <v>121561247</v>
       </c>
       <c r="B21" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,16 +2879,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2902,16 +2897,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625167</v>
+        <v>625210</v>
       </c>
       <c r="R21" t="n">
-        <v>7209946</v>
+        <v>7209708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 20434-2022 artfynd.xlsx
+++ b/artfynd/A 20434-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111336410</v>
+        <v>121561244</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Lill-Tjickuträsket, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625259.9138955096</v>
+        <v>625167</v>
       </c>
       <c r="R2" t="n">
-        <v>7209755.994336623</v>
+        <v>7209946</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,50 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561244</v>
+        <v>111336397</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625167</v>
+        <v>625081</v>
       </c>
       <c r="R3" t="n">
-        <v>7209946</v>
+        <v>7209864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,6 +855,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,6 +871,511 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111336409</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>625221</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7209758</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111336410</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>625259</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7209756</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111336411</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>625220</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7209755</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111336417</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>625114</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7209835</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111396307</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>625153</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7209819</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
